--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260729.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>594,720,000</t>
+          <t>597,220,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.23%</t>
+          <t>14.13%</t>
         </is>
       </c>
     </row>
@@ -633,56 +633,56 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>665,000,000</t>
+          <t>667,700,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.09%</t>
+          <t>12.08%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>179,050,000</t>
+          <t>894,977,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.70%</t>
+          <t>10.67%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>894,977,000</t>
+          <t>179,050,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>10.64%</t>
+          <t>10.66%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,189,910,000</t>
+          <t>1,191,070,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.70%</t>
+          <t>7.47%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>5.05%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>780,090,000</t>
+          <t>784,690,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.83%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.60%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>72,000,000</t>
+          <t>11,430,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>11,430,000</t>
+          <t>73,440,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1019,44 +1019,44 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -1117,56 +1117,56 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>76,800,000</t>
+          <t>77,400,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>8,504,000</t>
+          <t>12,278,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,278,000</t>
+          <t>8,504,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>15,470,000</t>
+          <t>13,450,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1342,24 +1342,24 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>13,450,000</t>
+          <t>15,470,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1452,51 +1452,51 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>29,006,000</t>
+          <t>20,540,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>20,540,000</t>
+          <t>29,006,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>4,698,243,549</t>
+          <t>2,953,879,726</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,111,177,436</t>
+          <t>1,432,101,436</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>-2,329,842,560</t>
+          <t>-1,956,744,548</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
